--- a/erp-server/erp-server-file/src/main/resources/excel/wms/pdaMoveInfo.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/pdaMoveInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22890" windowHeight="11265"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>单据单号</t>
   </si>
@@ -35,6 +35,12 @@
     <t>单据状态</t>
   </si>
   <si>
+    <t>来源单号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">来源类型 </t>
+  </si>
+  <si>
     <t>单据日期</t>
   </si>
   <si>
@@ -53,9 +59,15 @@
     <t>取货仓位</t>
   </si>
   <si>
+    <t>取货仓位库存状态</t>
+  </si>
+  <si>
     <t>上架仓位</t>
   </si>
   <si>
+    <t>上架仓位库存状态</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -77,6 +89,12 @@
     <t>{.approveStatusName}</t>
   </si>
   <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.sourceTypeName}</t>
+  </si>
+  <si>
     <t>{.billDate}</t>
   </si>
   <si>
@@ -95,7 +113,13 @@
     <t>{.outWarehouseLocationName}</t>
   </si>
   <si>
+    <t>{.outInventoryStatusName}</t>
+  </si>
+  <si>
     <t>{.inWarehouseLocationName}</t>
+  </si>
+  <si>
+    <t>{.inInventoryStatusName}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1291,25 +1315,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="26.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.875" customWidth="1"/>
-    <col min="11" max="11" width="21.375" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="20.875" customWidth="1"/>
-    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="3" max="6" width="16.875" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="25.5" style="3" customWidth="1"/>
+    <col min="11" max="12" width="26.25" style="3" customWidth="1"/>
+    <col min="13" max="13" width="22.625" customWidth="1"/>
+    <col min="14" max="14" width="16.875" customWidth="1"/>
+    <col min="15" max="15" width="21.375" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="20.875" customWidth="1"/>
+    <col min="18" max="18" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1331,19 +1356,19 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
@@ -1352,49 +1377,73 @@
       <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:14">
+    <row r="2" s="2" customFormat="1" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="M2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
